--- a/artfynd/A 42478-2025 artfynd.xlsx
+++ b/artfynd/A 42478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110386177</v>
+        <v>137518421</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>93498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,45 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598918</v>
+        <v>598768</v>
       </c>
       <c r="R4" t="n">
-        <v>7033648</v>
+        <v>7033880</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,17 +952,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Ådals-Liden</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +987,466 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137518421</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137518422</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80155</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598760</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7033891</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518422</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110386177</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598918</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033648</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/110386177</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137518425</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598860</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7033565</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518425</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137518423</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79559</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598763</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7033902</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518423</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1455,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42478-2025 artfynd.xlsx
+++ b/artfynd/A 42478-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>137518421</v>
       </c>
       <c r="B4" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137518422</v>
       </c>
       <c r="B5" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>137518425</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>137518423</v>
       </c>
       <c r="B8" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
